--- a/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.56314173348061</v>
+        <v>45.29468489131304</v>
       </c>
       <c r="M2" t="n">
-        <v>99.43129832136196</v>
+        <v>99.63291227204203</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06625934000913</v>
+        <v>88.01479612535253</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93056980158783</v>
+        <v>45.87687686063487</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228829062788457</v>
+        <v>2.228737810743256</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709614730872497</v>
+        <v>5.676251324127285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429430209294857</v>
+        <v>0.7429126035810856</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9733585371649</v>
+        <v>33.95523580242725</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17537896275634</v>
+        <v>34.17397976472993</v>
       </c>
       <c r="I3" t="n">
-        <v>6.592741144688168</v>
+        <v>6.594475047361936</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643393880809286</v>
+        <v>4.643203772381784</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93374065999086</v>
+        <v>11.98520387464748</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89905439202062</v>
+        <v>48.90121219166225</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7633648535993</v>
+        <v>106.7632929269446</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23369203721872</v>
+        <v>87.22181997741305</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73783654128272</v>
+        <v>42.72606070507301</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189149672157352</v>
+        <v>2.191119580819403</v>
       </c>
       <c r="E4" t="n">
-        <v>6.525552419935067</v>
+        <v>6.498270393123447</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445059794762775</v>
+        <v>0.7444761232815228</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36853774271589</v>
+        <v>33.38211506055391</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24727505590876</v>
+        <v>34.24590167095004</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505508795298628</v>
+        <v>5.506961378175206</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653162371726734</v>
+        <v>4.652975770509517</v>
       </c>
       <c r="K4" t="n">
-        <v>12.76630796278129</v>
+        <v>12.77818002258695</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31272379747243</v>
+        <v>44.31257940991333</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81686830153643</v>
+        <v>99.81682013757329</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.17801902559401</v>
+        <v>86.28220775654557</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53672680200693</v>
+        <v>42.64122468387957</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138028202607403</v>
+        <v>2.145988439611381</v>
       </c>
       <c r="E5" t="n">
-        <v>7.139179749472316</v>
+        <v>7.130637767275751</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458295223786702</v>
+        <v>0.7457983614988895</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58930884492222</v>
+        <v>32.69453371546963</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30815802941882</v>
+        <v>34.30672462894891</v>
       </c>
       <c r="I5" t="n">
-        <v>4.596080161927901</v>
+        <v>4.597285084372955</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661434514866689</v>
+        <v>4.661239759368059</v>
       </c>
       <c r="K5" t="n">
-        <v>13.82198097440598</v>
+        <v>13.71779224345444</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48836142371768</v>
+        <v>43.48801192327223</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84706920013059</v>
+        <v>99.84702885060624</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.9403486786659</v>
+        <v>85.19417430288028</v>
       </c>
       <c r="C6" t="n">
-        <v>42.01302043938695</v>
+        <v>42.26743664746441</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077946421097516</v>
+        <v>2.093495268898761</v>
       </c>
       <c r="E6" t="n">
-        <v>7.577863519551864</v>
+        <v>7.595685102305923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469522227817043</v>
+        <v>0.7469179590471683</v>
       </c>
       <c r="G6" t="n">
-        <v>31.67350065717664</v>
+        <v>31.89479047919831</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35980224795839</v>
+        <v>34.35822611616973</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835832217714138</v>
+        <v>3.836822133215594</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668451392385652</v>
+        <v>4.668237244044802</v>
       </c>
       <c r="K6" t="n">
-        <v>15.05965132133408</v>
+        <v>14.8058256971197</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7996593458921</v>
+        <v>42.7990352919611</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87233110661313</v>
+        <v>99.87229763654521</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.45111948270291</v>
+        <v>83.86881106751903</v>
       </c>
       <c r="C7" t="n">
-        <v>41.11978809932724</v>
+        <v>41.5384175370355</v>
       </c>
       <c r="D7" t="n">
-        <v>2.005632070706556</v>
+        <v>2.029350289956565</v>
       </c>
       <c r="E7" t="n">
-        <v>7.847582818800708</v>
+        <v>7.896522291108345</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479071551685508</v>
+        <v>0.7478683314635806</v>
       </c>
       <c r="G7" t="n">
-        <v>30.57123516978181</v>
+        <v>30.91752977359847</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40372913775333</v>
+        <v>34.4019432473247</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200613410688506</v>
+        <v>3.201420062419996</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674419719803443</v>
+        <v>4.674177071647378</v>
       </c>
       <c r="K7" t="n">
-        <v>16.54888051729708</v>
+        <v>16.13118893248097</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22478048843917</v>
+        <v>42.2238151378942</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89344910506348</v>
+        <v>99.89342160741066</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19385106257427</v>
+        <v>88.771365475775</v>
       </c>
       <c r="C8" t="n">
-        <v>43.35483408710914</v>
+        <v>43.87611247333519</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009867088810522</v>
+        <v>2.033650602346222</v>
       </c>
       <c r="E8" t="n">
-        <v>9.632588450226311</v>
+        <v>9.753230710140874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749486408107555</v>
+        <v>0.7494531083586987</v>
       </c>
       <c r="G8" t="n">
-        <v>31.05443859553607</v>
+        <v>31.43275411039957</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47637477294752</v>
+        <v>34.47484298450013</v>
       </c>
       <c r="I8" t="n">
-        <v>5.586805696274066</v>
+        <v>5.64335203278763</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684290050672219</v>
+        <v>4.684081927241866</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80614893742574</v>
+        <v>11.22863452422502</v>
       </c>
       <c r="L8" t="n">
-        <v>44.65318252004872</v>
+        <v>44.70753904490857</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81416554458359</v>
+        <v>99.81228604246877</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.20294590989288</v>
+        <v>87.06357580405528</v>
       </c>
       <c r="C9" t="n">
-        <v>42.23142062559268</v>
+        <v>43.04509775296837</v>
       </c>
       <c r="D9" t="n">
-        <v>1.919605206281377</v>
+        <v>1.956815796605401</v>
       </c>
       <c r="E9" t="n">
-        <v>9.977339556329186</v>
+        <v>10.16994962061238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508381235472512</v>
+        <v>0.7508049482807764</v>
       </c>
       <c r="G9" t="n">
-        <v>29.65980304768116</v>
+        <v>30.24517077962231</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53855368317355</v>
+        <v>34.5370276209157</v>
       </c>
       <c r="I9" t="n">
-        <v>4.664068020710014</v>
+        <v>4.71127611126385</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692738272170321</v>
+        <v>4.692530926754852</v>
       </c>
       <c r="K9" t="n">
-        <v>13.79705409010714</v>
+        <v>12.93642419594474</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81633623718146</v>
+        <v>43.86171827239835</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84481095288128</v>
+        <v>99.84324022131146</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.94866185546402</v>
+        <v>85.20136457351181</v>
       </c>
       <c r="C10" t="n">
-        <v>40.70108910450875</v>
+        <v>41.91487381891965</v>
       </c>
       <c r="D10" t="n">
-        <v>1.818280595184319</v>
+        <v>1.873693357249719</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09948327850339</v>
+        <v>10.39329676837387</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519986784063658</v>
+        <v>0.7519599542242115</v>
       </c>
       <c r="G10" t="n">
-        <v>28.09423737866353</v>
+        <v>28.9604037727877</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59193920669283</v>
+        <v>34.59015789431371</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8927309779738</v>
+        <v>3.932103112661266</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699991740039787</v>
+        <v>4.699749713901321</v>
       </c>
       <c r="K10" t="n">
-        <v>16.05133814453597</v>
+        <v>14.79863542648817</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11801530593556</v>
+        <v>43.15562197372377</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87044255498029</v>
+        <v>99.86913121913159</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.61438682434247</v>
+        <v>83.22752720256695</v>
       </c>
       <c r="C11" t="n">
-        <v>38.97038197991017</v>
+        <v>40.55164191400469</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714474765321334</v>
+        <v>1.78633116145914</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06427706956328</v>
+        <v>10.45554550294572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529963279924022</v>
+        <v>0.7529480986993237</v>
       </c>
       <c r="G11" t="n">
-        <v>26.49033442046019</v>
+        <v>27.61010573453976</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6378310876505</v>
+        <v>34.63561254016887</v>
       </c>
       <c r="I11" t="n">
-        <v>3.248246103402252</v>
+        <v>3.281058547883358</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706227049952515</v>
+        <v>4.705925616870772</v>
       </c>
       <c r="K11" t="n">
-        <v>18.38561317565754</v>
+        <v>16.77247279743305</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53587342837745</v>
+        <v>42.56666020209942</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89186858394515</v>
+        <v>99.89077491353716</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.1353145495214</v>
+        <v>81.12140791566938</v>
       </c>
       <c r="C12" t="n">
-        <v>36.99415560065536</v>
+        <v>38.95451378684128</v>
       </c>
       <c r="D12" t="n">
-        <v>1.605241326496342</v>
+        <v>1.693829188511252</v>
       </c>
       <c r="E12" t="n">
-        <v>9.874717289547856</v>
+        <v>10.37033886570441</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538558646638125</v>
+        <v>0.7537949930741068</v>
       </c>
       <c r="G12" t="n">
-        <v>24.80256952423638</v>
+        <v>26.18036565674896</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67736977453538</v>
+        <v>34.6745696814089</v>
       </c>
       <c r="I12" t="n">
-        <v>2.709961615892802</v>
+        <v>2.737290823508586</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711599154148829</v>
+        <v>4.711218706713166</v>
       </c>
       <c r="K12" t="n">
-        <v>20.8646854504786</v>
+        <v>18.87859208433063</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05092989043823</v>
+        <v>42.07575361360911</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90977094157219</v>
+        <v>99.90885948478102</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.62943284389816</v>
+        <v>78.96239487910135</v>
       </c>
       <c r="C13" t="n">
-        <v>34.90688585708403</v>
+        <v>37.21949494851358</v>
       </c>
       <c r="D13" t="n">
-        <v>1.49584349340272</v>
+        <v>1.599748156054248</v>
       </c>
       <c r="E13" t="n">
-        <v>9.578505050299087</v>
+        <v>10.17488070688062</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545971410796667</v>
+        <v>0.7545215502180038</v>
       </c>
       <c r="G13" t="n">
-        <v>23.11226457362337</v>
+        <v>24.72621913017169</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71146848966468</v>
+        <v>34.70799131002816</v>
       </c>
       <c r="I13" t="n">
-        <v>2.26052196408073</v>
+        <v>2.283274336886102</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716232131747918</v>
+        <v>4.715759688862523</v>
       </c>
       <c r="K13" t="n">
-        <v>23.37056715610184</v>
+        <v>21.03760512089864</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64727027526154</v>
+        <v>41.66686407437922</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92472328844741</v>
+        <v>99.92396414379145</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.41379468826298</v>
+        <v>85.09583284742607</v>
       </c>
       <c r="C14" t="n">
-        <v>39.17154320464396</v>
+        <v>40.92696066822771</v>
       </c>
       <c r="D14" t="n">
-        <v>1.497543934394118</v>
+        <v>1.601669530860911</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94402190391629</v>
+        <v>12.280612185572</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554549500124479</v>
+        <v>0.7554277670448128</v>
       </c>
       <c r="G14" t="n">
-        <v>25.0190517391114</v>
+        <v>26.33840644137187</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63144136735684</v>
+        <v>36.3321672117572</v>
       </c>
       <c r="I14" t="n">
-        <v>2.844687355894089</v>
+        <v>3.066126166789203</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721593437577801</v>
+        <v>4.721423544030079</v>
       </c>
       <c r="K14" t="n">
-        <v>16.58620531173704</v>
+        <v>14.90416715257393</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14753624189667</v>
+        <v>44.06679057857181</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90528475827766</v>
+        <v>99.89791839937345</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.54520322440763</v>
+        <v>84.50012797544318</v>
       </c>
       <c r="C15" t="n">
-        <v>38.74257652967534</v>
+        <v>40.7976683444607</v>
       </c>
       <c r="D15" t="n">
-        <v>1.465126063602364</v>
+        <v>1.578511741278618</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08093942339491</v>
+        <v>12.53793531833413</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561788269051026</v>
+        <v>0.7561899532023068</v>
       </c>
       <c r="G15" t="n">
-        <v>24.47745535052941</v>
+        <v>25.96619399394997</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66654161251378</v>
+        <v>36.37742665793468</v>
       </c>
       <c r="I15" t="n">
-        <v>2.372844279305168</v>
+        <v>2.557683103229065</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726117668156893</v>
+        <v>4.726187207514417</v>
       </c>
       <c r="K15" t="n">
-        <v>17.45479677559236</v>
+        <v>15.49987202455681</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72360760151305</v>
+        <v>43.61728945968279</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92098090678074</v>
+        <v>99.91482982870031</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.94873580107793</v>
+        <v>82.35334027056669</v>
       </c>
       <c r="C16" t="n">
-        <v>36.51279394656113</v>
+        <v>39.0472770662259</v>
       </c>
       <c r="D16" t="n">
-        <v>1.366205068125975</v>
+        <v>1.495258139319097</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59510361565149</v>
+        <v>12.23220212446186</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568027597433096</v>
+        <v>0.7568428863964267</v>
       </c>
       <c r="G16" t="n">
-        <v>22.82480967712586</v>
+        <v>24.59668933798526</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69679564576828</v>
+        <v>36.40883679407976</v>
       </c>
       <c r="I16" t="n">
-        <v>1.979001786267327</v>
+        <v>2.133242948346617</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730017248395686</v>
+        <v>4.730268039977667</v>
       </c>
       <c r="K16" t="n">
-        <v>20.05126419892207</v>
+        <v>17.64665972943331</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37002951342498</v>
+        <v>43.23501645147331</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93408765890818</v>
+        <v>99.92895324713253</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.58140186819446</v>
+        <v>83.91212000546162</v>
       </c>
       <c r="C17" t="n">
-        <v>37.71136787671739</v>
+        <v>40.18147895353776</v>
       </c>
       <c r="D17" t="n">
-        <v>1.367298284434926</v>
+        <v>1.496535527286548</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3522731655226</v>
+        <v>12.97257906414197</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574083416862497</v>
+        <v>0.7574894516756325</v>
       </c>
       <c r="G17" t="n">
-        <v>23.26456414235631</v>
+        <v>24.98920165066658</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14765026108034</v>
+        <v>36.81144013695407</v>
       </c>
       <c r="I17" t="n">
-        <v>1.958405537574971</v>
+        <v>2.150565101764096</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733802135539062</v>
+        <v>4.734309072972704</v>
       </c>
       <c r="K17" t="n">
-        <v>18.41859813180554</v>
+        <v>16.0878799945384</v>
       </c>
       <c r="L17" t="n">
-        <v>43.80480600132697</v>
+        <v>43.6590167366544</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93477200984989</v>
+        <v>99.92837568473057</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.05925274607624</v>
+        <v>81.78266014756507</v>
       </c>
       <c r="C18" t="n">
-        <v>35.49139558098949</v>
+        <v>38.38503543334142</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274932058976665</v>
+        <v>1.416806407376804</v>
       </c>
       <c r="E18" t="n">
-        <v>11.79001795793798</v>
+        <v>12.58036253569852</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579298682626753</v>
+        <v>0.7580431622215557</v>
       </c>
       <c r="G18" t="n">
-        <v>21.69295390834718</v>
+        <v>23.6578820671835</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17322891634018</v>
+        <v>36.83834860752004</v>
       </c>
       <c r="I18" t="n">
-        <v>1.633128359569838</v>
+        <v>1.793447603679921</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737061676641721</v>
+        <v>4.737769763884724</v>
       </c>
       <c r="K18" t="n">
-        <v>20.94074725392376</v>
+        <v>18.21733985243494</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51345701126522</v>
+        <v>43.33788679473019</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94559984617847</v>
+        <v>99.94026208050656</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.98494586827303</v>
+        <v>80.94253936713288</v>
       </c>
       <c r="C19" t="n">
-        <v>34.66148570088064</v>
+        <v>37.82206333700375</v>
       </c>
       <c r="D19" t="n">
-        <v>1.235956177712184</v>
+        <v>1.386049156147531</v>
       </c>
       <c r="E19" t="n">
-        <v>11.65764982716547</v>
+        <v>12.55650056064975</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583731754501623</v>
+        <v>0.7585100050383995</v>
       </c>
       <c r="G19" t="n">
-        <v>21.02977974949338</v>
+        <v>23.14429642943916</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19497124402874</v>
+        <v>36.86103559856341</v>
       </c>
       <c r="I19" t="n">
-        <v>1.368383347859572</v>
+        <v>1.495460085804641</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739832346563515</v>
+        <v>4.740687531489998</v>
       </c>
       <c r="K19" t="n">
-        <v>22.01505413172696</v>
+        <v>19.05746063286711</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27787405208884</v>
+        <v>43.07065804113803</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95441388469644</v>
+        <v>99.95018201100889</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.32922015351501</v>
+        <v>78.5360303070979</v>
       </c>
       <c r="C20" t="n">
-        <v>32.21608645782143</v>
+        <v>35.64654988093493</v>
       </c>
       <c r="D20" t="n">
-        <v>1.139773251612648</v>
+        <v>1.296796456467862</v>
       </c>
       <c r="E20" t="n">
-        <v>10.94059300856767</v>
+        <v>11.95575495260407</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587560389535193</v>
+        <v>0.7589114208436658</v>
       </c>
       <c r="G20" t="n">
-        <v>19.39322839920265</v>
+        <v>21.65395178375901</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21374906668748</v>
+        <v>36.88054305685593</v>
       </c>
       <c r="I20" t="n">
-        <v>1.140895145031533</v>
+        <v>1.246876256294443</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742225243459496</v>
+        <v>4.743196380272912</v>
       </c>
       <c r="K20" t="n">
-        <v>24.67077984648501</v>
+        <v>21.4639696929021</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07512304714189</v>
+        <v>42.84793986822394</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96198935144832</v>
+        <v>99.95845944206097</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.42454803748694</v>
+        <v>83.91099099560174</v>
       </c>
       <c r="C21" t="n">
-        <v>36.06306264316571</v>
+        <v>38.86180020545878</v>
       </c>
       <c r="D21" t="n">
-        <v>1.140505618481713</v>
+        <v>1.297788064577626</v>
       </c>
       <c r="E21" t="n">
-        <v>12.99500898625787</v>
+        <v>13.72472030985371</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592435813518396</v>
+        <v>0.7594917298935149</v>
       </c>
       <c r="G21" t="n">
-        <v>21.19147695409464</v>
+        <v>23.10951615722857</v>
       </c>
       <c r="H21" t="n">
-        <v>39.02344828416335</v>
+        <v>38.34775059245408</v>
       </c>
       <c r="I21" t="n">
-        <v>1.569592229688532</v>
+        <v>1.924900829759758</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745272383448998</v>
+        <v>4.746823311834468</v>
       </c>
       <c r="K21" t="n">
-        <v>18.57545196251305</v>
+        <v>16.08900900439828</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30919925004898</v>
+        <v>44.98507645480532</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94771385572776</v>
+        <v>99.93588566466238</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.29468489131304</v>
+        <v>45.71373406605944</v>
       </c>
       <c r="M2" t="n">
-        <v>99.63291227204203</v>
+        <v>98.86195930418873</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01479612535253</v>
+        <v>87.96447173803283</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87687686063487</v>
+        <v>45.88106558266273</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228737810743256</v>
+        <v>2.228605456312637</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676251324127285</v>
+        <v>5.675785785658221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429126035810856</v>
+        <v>0.7428684854375457</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95523580242725</v>
+        <v>33.9572373971583</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17397976472993</v>
+        <v>34.1719503301271</v>
       </c>
       <c r="I3" t="n">
-        <v>6.594475047361936</v>
+        <v>6.545096249354378</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643203772381784</v>
+        <v>4.64292803398466</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98520387464748</v>
+        <v>12.03552826196717</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90121219166225</v>
+        <v>48.848457569713</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632929269446</v>
+        <v>106.7650514143429</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22181997741305</v>
+        <v>86.99860572646587</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72606070507301</v>
+        <v>42.5476722587434</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191119580819403</v>
+        <v>2.181744607041332</v>
       </c>
       <c r="E4" t="n">
-        <v>6.498270393123447</v>
+        <v>6.467385956829349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444761232815228</v>
+        <v>0.7444241706012603</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38211506055391</v>
+        <v>33.24321914021164</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24590167095004</v>
+        <v>34.24351184765797</v>
       </c>
       <c r="I4" t="n">
-        <v>5.506961378175206</v>
+        <v>5.465668937866434</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652975770509517</v>
+        <v>4.652651066257876</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77818002258695</v>
+        <v>13.00139427353413</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31257940991333</v>
+        <v>44.26912523857374</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81682013757329</v>
+        <v>99.81819177085127</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.28220775654557</v>
+        <v>85.78194041275945</v>
       </c>
       <c r="C5" t="n">
-        <v>42.64122468387957</v>
+        <v>42.17922924679195</v>
       </c>
       <c r="D5" t="n">
-        <v>2.145988439611381</v>
+        <v>2.122136875307772</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130637767275751</v>
+        <v>7.051156277379199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457983614988895</v>
+        <v>0.7457440515298467</v>
       </c>
       <c r="G5" t="n">
-        <v>32.69453371546963</v>
+        <v>32.33497677212031</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30672462894891</v>
+        <v>34.30422637037294</v>
       </c>
       <c r="I5" t="n">
-        <v>4.597285084372955</v>
+        <v>4.562799743987839</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661239759368059</v>
+        <v>4.660900322061541</v>
       </c>
       <c r="K5" t="n">
-        <v>13.71779224345444</v>
+        <v>14.21805958724055</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48801192327223</v>
+        <v>43.45088702880454</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84702885060624</v>
+        <v>99.84817586283704</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.19417430288028</v>
+        <v>84.45160699407189</v>
       </c>
       <c r="C6" t="n">
-        <v>42.26743664746441</v>
+        <v>41.55740274431458</v>
       </c>
       <c r="D6" t="n">
-        <v>2.093495268898761</v>
+        <v>2.0572101755526</v>
       </c>
       <c r="E6" t="n">
-        <v>7.595685102305923</v>
+        <v>7.470101112499632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469179590471683</v>
+        <v>0.7468649417079003</v>
       </c>
       <c r="G6" t="n">
-        <v>31.89479047919831</v>
+        <v>31.34568934542244</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35822611616973</v>
+        <v>34.35578731856341</v>
       </c>
       <c r="I6" t="n">
-        <v>3.836822133215594</v>
+        <v>3.808048214651555</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668237244044802</v>
+        <v>4.667905885674376</v>
       </c>
       <c r="K6" t="n">
-        <v>14.8058256971197</v>
+        <v>15.54839300592808</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7990352919611</v>
+        <v>42.76745981242436</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87229763654521</v>
+        <v>99.87325556266703</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.86881106751903</v>
+        <v>82.7879055540277</v>
       </c>
       <c r="C7" t="n">
-        <v>41.5384175370355</v>
+        <v>40.48505972050661</v>
       </c>
       <c r="D7" t="n">
-        <v>2.029350289956565</v>
+        <v>1.975997905825237</v>
       </c>
       <c r="E7" t="n">
-        <v>7.896522291108345</v>
+        <v>7.704776942834012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478683314635806</v>
+        <v>0.7478204410100063</v>
       </c>
       <c r="G7" t="n">
-        <v>30.91752977359847</v>
+        <v>30.10825886400516</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4019432473247</v>
+        <v>34.39974028646029</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201420062419996</v>
+        <v>3.177433357580473</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674177071647378</v>
+        <v>4.673877756312539</v>
       </c>
       <c r="K7" t="n">
-        <v>16.13118893248097</v>
+        <v>17.21209444597232</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2238151378942</v>
+        <v>42.19706671644741</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89342160741066</v>
+        <v>99.89422088292632</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.771365475775</v>
+        <v>87.64404956633619</v>
       </c>
       <c r="C8" t="n">
-        <v>43.87611247333519</v>
+        <v>42.77710756769127</v>
       </c>
       <c r="D8" t="n">
-        <v>2.033650602346222</v>
+        <v>1.980220284599763</v>
       </c>
       <c r="E8" t="n">
-        <v>9.753230710140874</v>
+        <v>9.530068998584968</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494531083586987</v>
+        <v>0.749418408876252</v>
       </c>
       <c r="G8" t="n">
-        <v>31.43275411039957</v>
+        <v>30.60880743760036</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47484298450013</v>
+        <v>34.47324680830759</v>
       </c>
       <c r="I8" t="n">
-        <v>5.64335203278763</v>
+        <v>5.618422572890698</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684081927241866</v>
+        <v>4.683865055476574</v>
       </c>
       <c r="K8" t="n">
-        <v>11.22863452422502</v>
+        <v>12.35595043366381</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70753904490857</v>
+        <v>44.68006058071357</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81228604246877</v>
+        <v>99.81311858206865</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.06357580405528</v>
+        <v>85.59790129190316</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04509775296837</v>
+        <v>41.60270332368533</v>
       </c>
       <c r="D9" t="n">
-        <v>1.956815796605401</v>
+        <v>1.887462399125528</v>
       </c>
       <c r="E9" t="n">
-        <v>10.16994962061238</v>
+        <v>9.86542137238594</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508049482807764</v>
+        <v>0.7507872898733322</v>
       </c>
       <c r="G9" t="n">
-        <v>30.24517077962231</v>
+        <v>29.17502338999694</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5370276209157</v>
+        <v>34.53621533417327</v>
       </c>
       <c r="I9" t="n">
-        <v>4.71127611126385</v>
+        <v>4.690570944639797</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692530926754852</v>
+        <v>4.692420561708325</v>
       </c>
       <c r="K9" t="n">
-        <v>12.93642419594474</v>
+        <v>14.40209870809687</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86171827239835</v>
+        <v>43.83913067452641</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84324022131146</v>
+        <v>99.84393270630861</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.20136457351181</v>
+        <v>83.31072714825351</v>
       </c>
       <c r="C10" t="n">
-        <v>41.91487381891965</v>
+        <v>40.04298849448764</v>
       </c>
       <c r="D10" t="n">
-        <v>1.873693357249719</v>
+        <v>1.784776639820031</v>
       </c>
       <c r="E10" t="n">
-        <v>10.39329676837387</v>
+        <v>9.981190300505874</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519599542242115</v>
+        <v>0.7519633213358486</v>
       </c>
       <c r="G10" t="n">
-        <v>28.9604037727877</v>
+        <v>27.58778147675646</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59015789431371</v>
+        <v>34.59031278144903</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932103112661266</v>
+        <v>3.914931870037213</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699749713901321</v>
+        <v>4.699770758349053</v>
       </c>
       <c r="K10" t="n">
-        <v>14.79863542648817</v>
+        <v>16.68927285174651</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15562197372377</v>
+        <v>43.13744501641476</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86913121913159</v>
+        <v>99.8697063626489</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.22752720256695</v>
+        <v>80.93231151813018</v>
       </c>
       <c r="C11" t="n">
-        <v>40.55164191400469</v>
+        <v>38.27103664580007</v>
       </c>
       <c r="D11" t="n">
-        <v>1.78633116145914</v>
+        <v>1.679166688300283</v>
       </c>
       <c r="E11" t="n">
-        <v>10.45554550294572</v>
+        <v>9.935049027330619</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529480986993237</v>
+        <v>0.7529750880119849</v>
       </c>
       <c r="G11" t="n">
-        <v>27.61010573453976</v>
+        <v>25.95533952335246</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63561254016887</v>
+        <v>34.63685404855129</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281058547883358</v>
+        <v>3.266832842508641</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705925616870772</v>
+        <v>4.706094300074904</v>
       </c>
       <c r="K11" t="n">
-        <v>16.77247279743305</v>
+        <v>19.06768848186982</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56666020209942</v>
+        <v>42.5525267648291</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89077491353716</v>
+        <v>99.89125189249899</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>81.12140791566938</v>
+        <v>78.48843073654001</v>
       </c>
       <c r="C12" t="n">
-        <v>38.95451378684128</v>
+        <v>36.33237632908694</v>
       </c>
       <c r="D12" t="n">
-        <v>1.693829188511252</v>
+        <v>1.571754938543105</v>
       </c>
       <c r="E12" t="n">
-        <v>10.37033886570441</v>
+        <v>9.753782794790945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537949930741068</v>
+        <v>0.753846657021251</v>
       </c>
       <c r="G12" t="n">
-        <v>26.18036565674896</v>
+        <v>24.29504668097421</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6745696814089</v>
+        <v>34.67694622297753</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737290823508586</v>
+        <v>2.725511835850152</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711218706713166</v>
+        <v>4.711541606382816</v>
       </c>
       <c r="K12" t="n">
-        <v>18.87859208433063</v>
+        <v>21.51156926345998</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07575361360911</v>
+        <v>42.06530905071673</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90885948478102</v>
+        <v>99.90925464326365</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.96239487910135</v>
+        <v>76.10086753287852</v>
       </c>
       <c r="C13" t="n">
-        <v>37.21949494851358</v>
+        <v>34.36541117820276</v>
       </c>
       <c r="D13" t="n">
-        <v>1.599748156054248</v>
+        <v>1.467864235858884</v>
       </c>
       <c r="E13" t="n">
-        <v>10.17488070688062</v>
+        <v>9.487992295296037</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545215502180038</v>
+        <v>0.7545973653747039</v>
       </c>
       <c r="G13" t="n">
-        <v>24.72621913017169</v>
+        <v>22.6891796278241</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70799131002816</v>
+        <v>34.71147880723637</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283274336886102</v>
+        <v>2.273521667696538</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715759688862523</v>
+        <v>4.716233533591898</v>
       </c>
       <c r="K13" t="n">
-        <v>21.03760512089864</v>
+        <v>23.89913246712147</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66686407437922</v>
+        <v>41.65974769256881</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92396414379145</v>
+        <v>99.92429133789305</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85.09583284742607</v>
+        <v>83.06829803618444</v>
       </c>
       <c r="C14" t="n">
-        <v>40.92696066822771</v>
+        <v>38.77030795153426</v>
       </c>
       <c r="D14" t="n">
-        <v>1.601669530860911</v>
+        <v>1.469530842867908</v>
       </c>
       <c r="E14" t="n">
-        <v>12.280612185572</v>
+        <v>11.92237186797153</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554277670448128</v>
+        <v>0.75545413211607</v>
       </c>
       <c r="G14" t="n">
-        <v>26.33840644137187</v>
+        <v>24.66697075657858</v>
       </c>
       <c r="H14" t="n">
-        <v>36.3321672117572</v>
+        <v>36.70292000497374</v>
       </c>
       <c r="I14" t="n">
-        <v>3.066126166789203</v>
+        <v>2.829462105951167</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721423544030079</v>
+        <v>4.721588325725436</v>
       </c>
       <c r="K14" t="n">
-        <v>14.90416715257393</v>
+        <v>16.93170196381557</v>
       </c>
       <c r="L14" t="n">
-        <v>44.06679057857181</v>
+        <v>44.20378164499291</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89791839937345</v>
+        <v>99.90579156034273</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.50012797544318</v>
+        <v>82.29037097281631</v>
       </c>
       <c r="C15" t="n">
-        <v>40.7976683444607</v>
+        <v>38.42938138421474</v>
       </c>
       <c r="D15" t="n">
-        <v>1.578511741278618</v>
+        <v>1.440869675741596</v>
       </c>
       <c r="E15" t="n">
-        <v>12.53793531833413</v>
+        <v>12.08319903603083</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561899532023068</v>
+        <v>0.7561763620064028</v>
       </c>
       <c r="G15" t="n">
-        <v>25.96619399394997</v>
+        <v>24.18587559972266</v>
       </c>
       <c r="H15" t="n">
-        <v>36.37742665793468</v>
+        <v>36.73800876121079</v>
       </c>
       <c r="I15" t="n">
-        <v>2.557683103229065</v>
+        <v>2.36013927556403</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726187207514417</v>
+        <v>4.726102262540016</v>
       </c>
       <c r="K15" t="n">
-        <v>15.49987202455681</v>
+        <v>17.7096290271837</v>
       </c>
       <c r="L15" t="n">
-        <v>43.61728945968279</v>
+        <v>43.78239341899182</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91482982870031</v>
+        <v>99.92140383039026</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.35334027056669</v>
+        <v>79.73028711940597</v>
       </c>
       <c r="C16" t="n">
-        <v>39.0472770662259</v>
+        <v>36.23383394169728</v>
       </c>
       <c r="D16" t="n">
-        <v>1.495258139319097</v>
+        <v>1.344155977234346</v>
       </c>
       <c r="E16" t="n">
-        <v>12.23220212446186</v>
+        <v>11.60022041417658</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568428863964267</v>
+        <v>0.7567986510471459</v>
       </c>
       <c r="G16" t="n">
-        <v>24.59668933798526</v>
+        <v>22.56247723117727</v>
       </c>
       <c r="H16" t="n">
-        <v>36.40883679407976</v>
+        <v>36.76824199961851</v>
       </c>
       <c r="I16" t="n">
-        <v>2.133242948346617</v>
+        <v>1.968401277107454</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730268039977667</v>
+        <v>4.72999156904466</v>
       </c>
       <c r="K16" t="n">
-        <v>17.64665972943331</v>
+        <v>20.26971288059402</v>
       </c>
       <c r="L16" t="n">
-        <v>43.23501645147331</v>
+        <v>43.43089375338749</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92895324713253</v>
+        <v>99.93444057567881</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.91212000546162</v>
+        <v>81.43480730099634</v>
       </c>
       <c r="C17" t="n">
-        <v>40.18147895353776</v>
+        <v>37.4832964102693</v>
       </c>
       <c r="D17" t="n">
-        <v>1.496535527286548</v>
+        <v>1.345224472068174</v>
       </c>
       <c r="E17" t="n">
-        <v>12.97257906414197</v>
+        <v>12.38158361942685</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574894516756325</v>
+        <v>0.7574002445099487</v>
       </c>
       <c r="G17" t="n">
-        <v>24.98920165066658</v>
+        <v>23.02888425063636</v>
       </c>
       <c r="H17" t="n">
-        <v>36.81144013695407</v>
+        <v>37.24594144832147</v>
       </c>
       <c r="I17" t="n">
-        <v>2.150565101764096</v>
+        <v>1.942021737846354</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734309072972704</v>
+        <v>4.733751528187177</v>
       </c>
       <c r="K17" t="n">
-        <v>16.0878799945384</v>
+        <v>18.56519269900367</v>
       </c>
       <c r="L17" t="n">
-        <v>43.6590167366544</v>
+        <v>43.88682825024468</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92837568473057</v>
+        <v>99.93531735951764</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.78266014756507</v>
+        <v>79.0355042691105</v>
       </c>
       <c r="C18" t="n">
-        <v>38.38503543334142</v>
+        <v>35.38351479612306</v>
       </c>
       <c r="D18" t="n">
-        <v>1.416806407376804</v>
+        <v>1.258271014650571</v>
       </c>
       <c r="E18" t="n">
-        <v>12.58036253569852</v>
+        <v>11.8511645703741</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580431622215557</v>
+        <v>0.7579175550461741</v>
       </c>
       <c r="G18" t="n">
-        <v>23.6578820671835</v>
+        <v>21.54032888486605</v>
       </c>
       <c r="H18" t="n">
-        <v>36.83834860752004</v>
+        <v>37.2713807297087</v>
       </c>
       <c r="I18" t="n">
-        <v>1.793447603679921</v>
+        <v>1.619456795426319</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737769763884724</v>
+        <v>4.736984719038587</v>
       </c>
       <c r="K18" t="n">
-        <v>18.21733985243494</v>
+        <v>20.96449573088949</v>
       </c>
       <c r="L18" t="n">
-        <v>43.33788679473019</v>
+        <v>43.59804442471394</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94026208050656</v>
+        <v>99.9460549517265</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.94253936713288</v>
+        <v>78.05462050284341</v>
       </c>
       <c r="C19" t="n">
-        <v>37.82206333700375</v>
+        <v>34.64749584430796</v>
       </c>
       <c r="D19" t="n">
-        <v>1.386049156147531</v>
+        <v>1.223180048076271</v>
       </c>
       <c r="E19" t="n">
-        <v>12.55650056064975</v>
+        <v>11.74639324120877</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585100050383995</v>
+        <v>0.7583559401025584</v>
       </c>
       <c r="G19" t="n">
-        <v>23.14429642943916</v>
+        <v>20.93960697988902</v>
       </c>
       <c r="H19" t="n">
-        <v>36.86103559856341</v>
+        <v>37.29293876888318</v>
       </c>
       <c r="I19" t="n">
-        <v>1.495460085804641</v>
+        <v>1.354420899042623</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740687531489998</v>
+        <v>4.739724625640988</v>
       </c>
       <c r="K19" t="n">
-        <v>19.05746063286711</v>
+        <v>21.94537949715657</v>
       </c>
       <c r="L19" t="n">
-        <v>43.07065804113803</v>
+        <v>43.36200339370359</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95018201100889</v>
+        <v>99.95487873516812</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.5360303070979</v>
+        <v>75.46482896390259</v>
       </c>
       <c r="C20" t="n">
-        <v>35.64654988093493</v>
+        <v>32.26585868409171</v>
       </c>
       <c r="D20" t="n">
-        <v>1.296796456467862</v>
+        <v>1.130323989462561</v>
       </c>
       <c r="E20" t="n">
-        <v>11.95575495260407</v>
+        <v>11.04288953330484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589114208436658</v>
+        <v>0.7587342051530857</v>
       </c>
       <c r="G20" t="n">
-        <v>21.65395178375901</v>
+        <v>19.35000504341974</v>
       </c>
       <c r="H20" t="n">
-        <v>36.88054305685593</v>
+        <v>37.31154034450454</v>
       </c>
       <c r="I20" t="n">
-        <v>1.246876256294443</v>
+        <v>1.129247065851047</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743196380272912</v>
+        <v>4.742088782206783</v>
       </c>
       <c r="K20" t="n">
-        <v>21.4639696929021</v>
+        <v>24.5351710360974</v>
       </c>
       <c r="L20" t="n">
-        <v>42.84793986822394</v>
+        <v>43.16134747705969</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95845944206097</v>
+        <v>99.9623771972488</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.91099099560174</v>
+        <v>81.38371715046735</v>
       </c>
       <c r="C21" t="n">
-        <v>38.86180020545878</v>
+        <v>36.00052422521954</v>
       </c>
       <c r="D21" t="n">
-        <v>1.297788064577626</v>
+        <v>1.131040950288889</v>
       </c>
       <c r="E21" t="n">
-        <v>13.72472030985371</v>
+        <v>13.03941263503853</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594917298935149</v>
+        <v>0.7592154677890743</v>
       </c>
       <c r="G21" t="n">
-        <v>23.10951615722857</v>
+        <v>21.09369018740608</v>
       </c>
       <c r="H21" t="n">
-        <v>38.34775059245408</v>
+        <v>39.06661843185192</v>
       </c>
       <c r="I21" t="n">
-        <v>1.924900829759758</v>
+        <v>1.548642804411148</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746823311834468</v>
+        <v>4.745096673681712</v>
       </c>
       <c r="K21" t="n">
-        <v>16.08900900439828</v>
+        <v>18.61628284953267</v>
       </c>
       <c r="L21" t="n">
-        <v>44.98507645480532</v>
+        <v>45.33160422098123</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93588566466238</v>
+        <v>99.94841129573342</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_32_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71373406605944</v>
+        <v>43.85032022983046</v>
       </c>
       <c r="M2" t="n">
-        <v>98.86195930418873</v>
+        <v>95.58971137223364</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96447173803283</v>
+        <v>81.49948052597763</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88106558266273</v>
+        <v>43.25503608153317</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228605456312637</v>
+        <v>2.180652049208546</v>
       </c>
       <c r="E3" t="n">
-        <v>5.675785785658221</v>
+        <v>4.164845611718405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428684854375457</v>
+        <v>0.7376489107379759</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9572373971583</v>
+        <v>32.80064124017856</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1719503301271</v>
+        <v>33.93184989394689</v>
       </c>
       <c r="I3" t="n">
-        <v>6.545096249354378</v>
+        <v>3.0735371280749</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64292803398466</v>
+        <v>4.610305692112349</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03552826196717</v>
+        <v>18.50051947402239</v>
       </c>
       <c r="L3" t="n">
-        <v>48.848457569713</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650514143429</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99860572646587</v>
+        <v>88.54720710869296</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5476722587434</v>
+        <v>42.79491876581891</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181744607041332</v>
+        <v>2.186395003054078</v>
       </c>
       <c r="E4" t="n">
-        <v>6.467385956829349</v>
+        <v>6.510341693013691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444241706012603</v>
+        <v>0.7395915790559741</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24321914021164</v>
+        <v>33.47129496520525</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24351184765797</v>
+        <v>34.0212126365748</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465668937866434</v>
+        <v>6.995923862689327</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652651066257876</v>
+        <v>4.622447369099837</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00139427353413</v>
+        <v>11.45279289130703</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26912523857374</v>
+        <v>45.51970341523488</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81819177085127</v>
+        <v>99.76741507236082</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.78194041275945</v>
+        <v>87.42331483248016</v>
       </c>
       <c r="C5" t="n">
-        <v>42.17922924679195</v>
+        <v>42.75538705615635</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122136875307772</v>
+        <v>2.132862743454193</v>
       </c>
       <c r="E5" t="n">
-        <v>7.051156277379199</v>
+        <v>7.324761581778048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457440515298467</v>
+        <v>0.7412392622769338</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33497677212031</v>
+        <v>32.65177513977626</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30422637037294</v>
+        <v>34.09700606473896</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562799743987839</v>
+        <v>5.842924651224938</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660900322061541</v>
+        <v>4.632745389230836</v>
       </c>
       <c r="K5" t="n">
-        <v>14.21805958724055</v>
+        <v>12.57668516751985</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45088702880454</v>
+        <v>44.47359655791575</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84817586283704</v>
+        <v>99.80566878159195</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.45160699407189</v>
+        <v>86.04920958345447</v>
       </c>
       <c r="C6" t="n">
-        <v>41.55740274431458</v>
+        <v>42.28805079092989</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0572101755526</v>
+        <v>2.067162626497637</v>
       </c>
       <c r="E6" t="n">
-        <v>7.470101112499632</v>
+        <v>7.912182506942357</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468649417079003</v>
+        <v>0.7426400077952824</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34568934542244</v>
+        <v>31.64597884458276</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35578731856341</v>
+        <v>34.16144035858299</v>
       </c>
       <c r="I6" t="n">
-        <v>3.808048214651555</v>
+        <v>4.878305190332923</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667905885674376</v>
+        <v>4.641500048720514</v>
       </c>
       <c r="K6" t="n">
-        <v>15.54839300592808</v>
+        <v>13.95079041654553</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76745981242436</v>
+        <v>43.59885532999057</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87325556266703</v>
+        <v>99.83769653746599</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.7879055540277</v>
+        <v>84.40633227657761</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48505972050661</v>
+        <v>41.40262906648744</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975997905825237</v>
+        <v>1.988768232648412</v>
       </c>
       <c r="E7" t="n">
-        <v>7.704776942834012</v>
+        <v>8.290755390092361</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478204410100063</v>
+        <v>0.7438341816772625</v>
       </c>
       <c r="G7" t="n">
-        <v>30.10825886400516</v>
+        <v>30.44584717739518</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39974028646029</v>
+        <v>34.21637235715407</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177433357580473</v>
+        <v>4.071791302127451</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673877756312539</v>
+        <v>4.64896363548289</v>
       </c>
       <c r="K7" t="n">
-        <v>17.21209444597232</v>
+        <v>15.59366772342237</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19706671644741</v>
+        <v>42.86819473258094</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89422088292632</v>
+        <v>99.86449152249075</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.64404956633619</v>
+        <v>82.62039948286917</v>
       </c>
       <c r="C8" t="n">
-        <v>42.77710756769127</v>
+        <v>40.24879875784469</v>
       </c>
       <c r="D8" t="n">
-        <v>1.980220284599763</v>
+        <v>1.904161378100703</v>
       </c>
       <c r="E8" t="n">
-        <v>9.530068998584968</v>
+        <v>8.504349077680066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749418408876252</v>
+        <v>0.7448538684757605</v>
       </c>
       <c r="G8" t="n">
-        <v>30.60880743760036</v>
+        <v>29.15060959192283</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47324680830759</v>
+        <v>34.26327794988498</v>
       </c>
       <c r="I8" t="n">
-        <v>5.618422572890698</v>
+        <v>3.397810938831333</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683865055476574</v>
+        <v>4.655336677973503</v>
       </c>
       <c r="K8" t="n">
-        <v>12.35595043366381</v>
+        <v>17.37960051713082</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68006058071357</v>
+        <v>42.25849541107651</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81311858206865</v>
+        <v>99.88689468605202</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.59790129190316</v>
+        <v>80.76374942201845</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60270332368533</v>
+        <v>38.91924204127741</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887462399125528</v>
+        <v>1.816915636768679</v>
       </c>
       <c r="E9" t="n">
-        <v>9.86542137238594</v>
+        <v>8.587163235365866</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507872898733322</v>
+        <v>0.7457253519267292</v>
       </c>
       <c r="G9" t="n">
-        <v>29.17502338999694</v>
+        <v>27.81497356160668</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53621533417327</v>
+        <v>34.30336618862954</v>
       </c>
       <c r="I9" t="n">
-        <v>4.690570944639797</v>
+        <v>2.834821998178899</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692420561708325</v>
+        <v>4.660783449542057</v>
       </c>
       <c r="K9" t="n">
-        <v>14.40209870809687</v>
+        <v>19.23625057798155</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83913067452641</v>
+        <v>41.75012374355126</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84393270630861</v>
+        <v>99.90561636281022</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.31072714825351</v>
+        <v>85.5908496748614</v>
       </c>
       <c r="C10" t="n">
-        <v>40.04298849448764</v>
+        <v>42.31362345421683</v>
       </c>
       <c r="D10" t="n">
-        <v>1.784776639820031</v>
+        <v>1.818883137958572</v>
       </c>
       <c r="E10" t="n">
-        <v>9.981190300505874</v>
+        <v>10.50440963300346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519633213358486</v>
+        <v>0.7465328828255546</v>
       </c>
       <c r="G10" t="n">
-        <v>27.58778147675646</v>
+        <v>29.28961836733401</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59031278144903</v>
+        <v>35.78503714348334</v>
       </c>
       <c r="I10" t="n">
-        <v>3.914931870037213</v>
+        <v>2.780537992596751</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699770758349053</v>
+        <v>4.665830517659717</v>
       </c>
       <c r="K10" t="n">
-        <v>16.68927285174651</v>
+        <v>14.4091503251386</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13744501641476</v>
+        <v>43.18464187860251</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8697063626489</v>
+        <v>99.90741565795796</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.93231151813018</v>
+        <v>85.27529632776238</v>
       </c>
       <c r="C11" t="n">
-        <v>38.27103664580007</v>
+        <v>42.32600415927745</v>
       </c>
       <c r="D11" t="n">
-        <v>1.679166688300283</v>
+        <v>1.799586941761371</v>
       </c>
       <c r="E11" t="n">
-        <v>9.935049027330619</v>
+        <v>10.81622334578348</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529750880119849</v>
+        <v>0.7472323961714966</v>
       </c>
       <c r="G11" t="n">
-        <v>25.95533952335246</v>
+        <v>29.00262162378893</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63685404855129</v>
+        <v>35.8422997231383</v>
       </c>
       <c r="I11" t="n">
-        <v>3.266832842508641</v>
+        <v>2.39712982104695</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706094300074904</v>
+        <v>4.670202476071855</v>
       </c>
       <c r="K11" t="n">
-        <v>19.06768848186982</v>
+        <v>14.72470367223762</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5525267648291</v>
+        <v>42.86946264266933</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89125189249899</v>
+        <v>99.9201704741844</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.48843073654001</v>
+        <v>83.38883866162102</v>
       </c>
       <c r="C12" t="n">
-        <v>36.33237632908694</v>
+        <v>40.81214133873154</v>
       </c>
       <c r="D12" t="n">
-        <v>1.571754938543105</v>
+        <v>1.719389194661288</v>
       </c>
       <c r="E12" t="n">
-        <v>9.753782794790945</v>
+        <v>10.66740419289595</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753846657021251</v>
+        <v>0.7478295466002014</v>
       </c>
       <c r="G12" t="n">
-        <v>24.29504668097421</v>
+        <v>27.71013340871693</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67694622297753</v>
+        <v>35.87094308061999</v>
       </c>
       <c r="I12" t="n">
-        <v>2.725511835850152</v>
+        <v>1.999204571875403</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711541606382816</v>
+        <v>4.67393466625126</v>
       </c>
       <c r="K12" t="n">
-        <v>21.51156926345998</v>
+        <v>16.61116133837899</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06530905071673</v>
+        <v>42.51011038341594</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90925464326365</v>
+        <v>99.93341306052648</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.10086753287852</v>
+        <v>84.56092761076719</v>
       </c>
       <c r="C13" t="n">
-        <v>34.36541117820276</v>
+        <v>41.80187650441738</v>
       </c>
       <c r="D13" t="n">
-        <v>1.467864235858884</v>
+        <v>1.720628349108258</v>
       </c>
       <c r="E13" t="n">
-        <v>9.487992295296037</v>
+        <v>11.3063536117963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545973653747039</v>
+        <v>0.74836850328966</v>
       </c>
       <c r="G13" t="n">
-        <v>22.6891796278241</v>
+        <v>28.05665242540867</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71147880723637</v>
+        <v>36.22334354848475</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273521667696538</v>
+        <v>1.828278027119179</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716233533591898</v>
+        <v>4.677303145560376</v>
       </c>
       <c r="K13" t="n">
-        <v>23.89913246712147</v>
+        <v>15.43907238923281</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65974769256881</v>
+        <v>42.69815239481625</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92429133789305</v>
+        <v>99.93910128846643</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.06829803618444</v>
+        <v>82.67681632163895</v>
       </c>
       <c r="C14" t="n">
-        <v>38.77030795153426</v>
+        <v>40.20181910424121</v>
       </c>
       <c r="D14" t="n">
-        <v>1.469530842867908</v>
+        <v>1.642728741910003</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92237186797153</v>
+        <v>11.04855412986301</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75545413211607</v>
+        <v>0.7488284826546372</v>
       </c>
       <c r="G14" t="n">
-        <v>24.66697075657858</v>
+        <v>26.786417511303</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70292000497374</v>
+        <v>36.24560796833879</v>
       </c>
       <c r="I14" t="n">
-        <v>2.829462105951167</v>
+        <v>1.524501470978043</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721588325725436</v>
+        <v>4.680178016591483</v>
       </c>
       <c r="K14" t="n">
-        <v>16.93170196381557</v>
+        <v>17.32318367836103</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20378164499291</v>
+        <v>42.42421171664444</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90579156034273</v>
+        <v>99.94921449924668</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.29037097281631</v>
+        <v>81.82512073577372</v>
       </c>
       <c r="C15" t="n">
-        <v>38.42938138421474</v>
+        <v>39.55308354462565</v>
       </c>
       <c r="D15" t="n">
-        <v>1.440869675741596</v>
+        <v>1.6065228470692</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08319903603083</v>
+        <v>11.02229556021011</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561763620064028</v>
+        <v>0.7492261232068798</v>
       </c>
       <c r="G15" t="n">
-        <v>24.18587559972266</v>
+        <v>26.19604236850951</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73800876121079</v>
+        <v>36.26485499740184</v>
       </c>
       <c r="I15" t="n">
-        <v>2.36013927556403</v>
+        <v>1.303515569333193</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726102262540016</v>
+        <v>4.682663270042998</v>
       </c>
       <c r="K15" t="n">
-        <v>17.7096290271837</v>
+        <v>18.17487926422627</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78239341899182</v>
+        <v>42.22860973288299</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92140383039026</v>
+        <v>99.9565725417349</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.73028711940597</v>
+        <v>79.43203216685578</v>
       </c>
       <c r="C16" t="n">
-        <v>36.23383394169728</v>
+        <v>37.36204215915181</v>
       </c>
       <c r="D16" t="n">
-        <v>1.344155977234346</v>
+        <v>1.508187418366421</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60022041417658</v>
+        <v>10.528746110105</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567986510471459</v>
+        <v>0.7495678106165624</v>
       </c>
       <c r="G16" t="n">
-        <v>22.56247723117727</v>
+        <v>24.59257992082446</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76824199961851</v>
+        <v>36.28139372180395</v>
       </c>
       <c r="I16" t="n">
-        <v>1.968401277107454</v>
+        <v>1.08675836878587</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72999156904466</v>
+        <v>4.684798816353515</v>
       </c>
       <c r="K16" t="n">
-        <v>20.26971288059402</v>
+        <v>20.56796783314421</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43089375338749</v>
+        <v>42.03378124188917</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93444057567881</v>
+        <v>99.96379123418519</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.43480730099634</v>
+        <v>83.99568637004711</v>
       </c>
       <c r="C17" t="n">
-        <v>37.4832964102693</v>
+        <v>40.4278522566846</v>
       </c>
       <c r="D17" t="n">
-        <v>1.345224472068174</v>
+        <v>1.508866415438263</v>
       </c>
       <c r="E17" t="n">
-        <v>12.38158361942685</v>
+        <v>12.15309670696901</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574002445099487</v>
+        <v>0.7499052715596507</v>
       </c>
       <c r="G17" t="n">
-        <v>23.02888425063636</v>
+        <v>26.03418477924096</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24594144832147</v>
+        <v>37.72826097019104</v>
       </c>
       <c r="I17" t="n">
-        <v>1.942021737846354</v>
+        <v>1.134464279400361</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733751528187177</v>
+        <v>4.686907947247817</v>
       </c>
       <c r="K17" t="n">
-        <v>18.56519269900367</v>
+        <v>16.00431362995291</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88682825024468</v>
+        <v>43.53003565452672</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93531735951764</v>
+        <v>99.96220154116422</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.0355042691105</v>
+        <v>85.48858101651</v>
       </c>
       <c r="C18" t="n">
-        <v>35.38351479612306</v>
+        <v>41.12823410899938</v>
       </c>
       <c r="D18" t="n">
-        <v>1.258271014650571</v>
+        <v>1.509974720255676</v>
       </c>
       <c r="E18" t="n">
-        <v>11.8511645703741</v>
+        <v>12.72180112126396</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579175550461741</v>
+        <v>0.7504560980719046</v>
       </c>
       <c r="G18" t="n">
-        <v>21.54032888486605</v>
+        <v>26.17621201404902</v>
       </c>
       <c r="H18" t="n">
-        <v>37.2713807297087</v>
+        <v>37.75597343894112</v>
       </c>
       <c r="I18" t="n">
-        <v>1.619456795426319</v>
+        <v>1.883813010978931</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736984719038587</v>
+        <v>4.690350612949404</v>
       </c>
       <c r="K18" t="n">
-        <v>20.96449573088949</v>
+        <v>14.51141898349</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59804442471394</v>
+        <v>44.29759923041155</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9460549517265</v>
+        <v>99.93725232290092</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.05462050284341</v>
+        <v>82.7568778469203</v>
       </c>
       <c r="C19" t="n">
-        <v>34.64749584430796</v>
+        <v>38.68838148002015</v>
       </c>
       <c r="D19" t="n">
-        <v>1.223180048076271</v>
+        <v>1.408786617965831</v>
       </c>
       <c r="E19" t="n">
-        <v>11.74639324120877</v>
+        <v>12.13107990020939</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583559401025584</v>
+        <v>0.7509309204522641</v>
       </c>
       <c r="G19" t="n">
-        <v>20.93960697988902</v>
+        <v>24.42206263438937</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29293876888318</v>
+        <v>37.7798620864278</v>
       </c>
       <c r="I19" t="n">
-        <v>1.354420899042623</v>
+        <v>1.570837434648997</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739724625640988</v>
+        <v>4.693318252826651</v>
       </c>
       <c r="K19" t="n">
-        <v>21.94537949715657</v>
+        <v>17.2431221530797</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36200339370359</v>
+        <v>44.0161682277063</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95487873516812</v>
+        <v>99.94767186080614</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.46482896390259</v>
+        <v>79.77379817765819</v>
       </c>
       <c r="C20" t="n">
-        <v>32.26585868409171</v>
+        <v>35.94795226967823</v>
       </c>
       <c r="D20" t="n">
-        <v>1.130323989462561</v>
+        <v>1.298793413995397</v>
       </c>
       <c r="E20" t="n">
-        <v>11.04288953330484</v>
+        <v>11.40221825551205</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587342051530857</v>
+        <v>0.751341886621847</v>
       </c>
       <c r="G20" t="n">
-        <v>19.35000504341974</v>
+        <v>22.51527215067378</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31154034450454</v>
+        <v>37.80053808309561</v>
       </c>
       <c r="I20" t="n">
-        <v>1.129247065851047</v>
+        <v>1.309747596372976</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742088782206783</v>
+        <v>4.695886791386544</v>
       </c>
       <c r="K20" t="n">
-        <v>24.5351710360974</v>
+        <v>20.22620182234181</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16134747705969</v>
+        <v>43.78221153479528</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9623771972488</v>
+        <v>99.95636562681531</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.38371715046735</v>
+        <v>76.85699629590982</v>
       </c>
       <c r="C21" t="n">
-        <v>36.00052422521954</v>
+        <v>33.2327332134398</v>
       </c>
       <c r="D21" t="n">
-        <v>1.131040950288889</v>
+        <v>1.191784519904684</v>
       </c>
       <c r="E21" t="n">
-        <v>13.03941263503853</v>
+        <v>10.64477357907204</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592154677890743</v>
+        <v>0.7516977185664327</v>
       </c>
       <c r="G21" t="n">
-        <v>21.09369018740608</v>
+        <v>20.66021626031216</v>
       </c>
       <c r="H21" t="n">
-        <v>39.06661843185192</v>
+        <v>37.81844023817573</v>
       </c>
       <c r="I21" t="n">
-        <v>1.548642804411148</v>
+        <v>1.091973238838556</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745096673681712</v>
+        <v>4.698110741040205</v>
       </c>
       <c r="K21" t="n">
-        <v>18.61628284953267</v>
+        <v>23.14300370409021</v>
       </c>
       <c r="L21" t="n">
-        <v>45.33160422098123</v>
+        <v>43.58788120479296</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94841129573342</v>
+        <v>99.96361812232297</v>
       </c>
     </row>
   </sheetData>
